--- a/www/download/COUNTRY.GRC.WIOD16.xlsx
+++ b/www/download/COUNTRY.GRC.WIOD16.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>Grécia</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,1848 +852,3409 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1.0684315082037</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>1.11655917853443</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>1.05755630598782</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>0.883993497633862</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>0.803917957079311</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.803800682746865</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>0.796425776785814</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>0.72967807391736</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.679916617518272</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>0.716959318915958</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>0.754319705512082</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>0.718367131316809</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.778319525669977</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.752991091907422</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>0.752719981748076</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>4.308</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>4.328</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.434</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>4.496</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4.604</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>4.648</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>4.731</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>4.795</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>4.856</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>4.829</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>4.706</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>4.382</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>4.105</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>3.957</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>3.963</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2.681</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2.741</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>2.853</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2.916</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.014</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2.952</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>3.07</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>3.151</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>3.215</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>3.191</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>3.15</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>2.92</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>2.716</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>2.622</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.625</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>8733.793</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>8744.552</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>8938.064</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>9052.748</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>9228.506</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>9814.808</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>9900.977</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>10052.118</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>10122.079</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>9982.986</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>9297.616</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>8652.106</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>8042.358</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>7729.316</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>7625.096</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5318.839</t>
+          <t>8318946719.51216</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5428.968</t>
+          <t>8151126368.39072</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5635.053</t>
+          <t>7924233264.70403</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>5757.773</t>
+          <t>8147847456.86537</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5916.714</t>
+          <t>7898670017.35487</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>6109.817</t>
+          <t>8575308523.91725</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6303.115</t>
+          <t>8841023825.50706</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>6480.266</t>
+          <t>9099908404.18058</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>6592.1</t>
+          <t>8779354440.15689</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>6491.208</t>
+          <t>8472324945.68901</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>6130.236</t>
+          <t>7689882927.4262</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>5668.764</t>
+          <t>7467864740.24912</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>5286.824</t>
+          <t>6653743434.54132</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>5076.474</t>
+          <t>6823455129.33112</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>5009.031</t>
+          <t>7173883404.09946</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2345803714.04368</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2317502714.19332</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>2511440257.62385</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>2776061383.21948</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2894915552.00543</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>3071620395.78496</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>3237723722.59939</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>3315986252.67453</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>3329865978.26457</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>3259654351.8545</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2815500602.04227</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>2629410281.00747</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>2151833975.92363</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>2026144927.01421</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2063891440.45435</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2656516.84612405</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2820087.77441248</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>2418772.74087022</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>1863361.41207618</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1581500.42107634</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>1631855.54164856</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>1439213.22032309</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>1277977.63359253</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>1020233.96946193</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1139902.9051708</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1139804.7473169</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1118802.87461554</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1173536.34011791</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>1183681.87190319</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>1204449.57841463</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>35211.2086133608</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>34307.8097994901</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>34234.0093277242</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>37292.0199171438</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>40505.8984520046</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>47195.2940028985</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>49509.662286524</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>56657.6731036148</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>61254.9889868296</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>55478.5945922978</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>54638.5159491973</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>52238.3918522686</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>46245.0922292278</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>44529.0929144363</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>44259.6001009634</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>67594.4882074091</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>65608.3648199722</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>64164.9241404664</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>71801.029082782</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>76954.0930010286</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>89701.8522515634</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>97700.5269186955</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>113540.423220784</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>118895.640490919</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>104415.262259344</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>104996.44420376</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>108283.464217097</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>94004.0928700795</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>96305.9616278859</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>101720.927120836</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>1.26738455061588</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1.34259423592076</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.24375347289029</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>1.07407993022205</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>1.04382960183458</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>0.98911864512432</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0.946773702772757</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0.954249838874724</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>0.979689315735046</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>0.991379330236961</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1.17731649410884</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1.15590702635725</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1.45689214835022</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>1.50548439665708</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>1.4269838043891</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>27498.0680600712</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>28405.7394074023</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>30291.1645184171</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>32181.0252369924</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>33771.0162357611</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>36503.9498996808</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>35671.0771920439</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>41993.8572544497</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>47908.6244343292</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>48370.4796360053</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>54751.8200827573</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>53820.7182834728</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>49928.3696860019</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>50351.378700188</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>51221.0701951072</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.0684315082037</t>
+          <t>874.992992772565</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.11655917853443</t>
+          <t>845.631080579634</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.05755630598782</t>
+          <t>880.369984198833</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.883993497633862</t>
+          <t>951.967636291758</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.803917957079311</t>
+          <t>960.508686969691</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.803800682746865</t>
+          <t>1040.36322233567</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.796425776785814</t>
+          <t>1054.66061741003</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.72967807391736</t>
+          <t>1052.2965142294</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679916617518272</t>
+          <t>1035.76358079579</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716959318915958</t>
+          <t>1021.57582302127</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.754319705512082</t>
+          <t>893.804039987769</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.718367131316809</t>
+          <t>900.538485594137</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.778319525669977</t>
+          <t>792.353484644621</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.752991091907422</t>
+          <t>772.792084602174</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.752719981748076</t>
+          <t>786.193442883452</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>10419435.2240682</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>-237656403.532794</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>-281451740.343182</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>-70166985.3341089</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>561942342.500826</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>979040138.892159</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>829582542.007762</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>1047495260.14171</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>1136169515.78957</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>651708440.731811</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>831138389.647498</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>1135155047.54222</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>898009865.038784</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>1293132226.4928</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>1602103649.80358</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>784237750.398779</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>693225881.028645</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>624957635.380345</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>948540872.625306</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.111</t>
+          <t>1357241794.29435</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1682912420.44986</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>1745906677.37042</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1925428046.37126</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>2056583620.37055</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>1251991514.38916</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>0.148</t>
+          <t>1374742485.43037</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>1661939205.47378</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>1529584525.53619</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>0.106</t>
+          <t>1832849155.63107</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>0.103</t>
+          <t>2049876131.90379</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>-773818315.174711</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.452</t>
+          <t>-930882284.561438</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.484</t>
+          <t>-906409375.723526</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.516</t>
+          <t>-1018707857.95941</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>-795299451.793525</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>-703872281.557703</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>-916324135.362662</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>-877932786.229543</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-920414104.580981</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>-600283073.65735</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-543604095.782873</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.667</t>
+          <t>-526784157.931556</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>-631574660.49741</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>-539716929.138272</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>-447772482.100218</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>1983.94559370967</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>1980.9704950813</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>1975.3332094745</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>1974.45696865366</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.388</t>
+          <t>1963.11608724792</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2069.4058832495</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.444</t>
+          <t>2053.18555532392</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>2056.45029338123</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>2050.4900945289</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.524</t>
+          <t>2034.34497823437</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>1946.09427876648</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1941.47724859752</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>1946.72705514131</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>1936.21850983084</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>1908.07875299504</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>2027.28637606053</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>2020.26878127316</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.138</t>
+          <t>2015.66510821882</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>2013.63691914004</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>2004.41041459596</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>2111.53795478465</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>2092.64583181428</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.281</t>
+          <t>2096.30933053153</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>2084.27617283644</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>2067.28607191746</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>1975.89978079018</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>1974.52366320759</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>1959.03254664942</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>0.212</t>
+          <t>1953.16919532044</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>1924.25620190389</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>17296.3630154733</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>16965.4942745521</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>17525.455300482</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>24028.4085315402</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>35641.3873165872</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>38453.3064095924</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>42527.8025557338</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>55560.3243234167</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>67039.3861701338</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>48797.7438626878</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>51213.5981828547</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>55467.5641751503</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>51378.2303984235</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>53289.2475678248</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>56260.5926492155</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>774950170.684812</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>775993199.689139</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>697915535.60067</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>802126462.44901</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>843934681.094725</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>937723925.013008</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>1050504542.43107</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>1172646980.08328</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>1200618240.87703</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1051662425.88821</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1178513948.67571</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1371136170.03141</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>1236373248.78117</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>1439138231.14257</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>1667792868.18326</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>41848.9676311744</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>41750.8755920898</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>43019.5810472635</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>54879.1881393896</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>64128.3274303496</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>66958.6023109213</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>79375.2842400915</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>101307.250030754</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>115278.828049353</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>86142.4329667416</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>82902.5894747711</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>84338.8445138096</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>73337.6653502401</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>71797.2792728057</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>74421.7201028144</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>8733.793</t>
+          <t>4578770304.48688</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8744.552</t>
+          <t>4506225742.33378</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8938.064</t>
+          <t>4533142148.40183</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>9052.748</t>
+          <t>5425800214.99661</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>9228.506</t>
+          <t>5336931934.28302</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>9814.808</t>
+          <t>5511055797.33279</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9900.977</t>
+          <t>6108960315.49421</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>10052.118</t>
+          <t>6694223648.37343</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>10122.079</t>
+          <t>6489792898.40008</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>9982.986</t>
+          <t>5338870392.91122</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>9297.616</t>
+          <t>4750204373.204</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>8652.106</t>
+          <t>4875160238.65706</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>8042.358</t>
+          <t>3955458217.73552</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>7729.316</t>
+          <t>4275657136.36654</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>7625.096</t>
+          <t>4769570993.74487</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5318.839</t>
+          <t>-24552.6046157011</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5428.968</t>
+          <t>-24785.3813175377</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5635.053</t>
+          <t>-25494.1257467815</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>5757.773</t>
+          <t>-30850.7796078493</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5916.714</t>
+          <t>-28486.9401137625</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>6109.817</t>
+          <t>-28505.2959013288</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>6303.115</t>
+          <t>-36847.4816843577</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>6480.266</t>
+          <t>-45746.925707337</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>6592.1</t>
+          <t>-48239.4418792193</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>6491.208</t>
+          <t>-37344.6891040538</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>6130.236</t>
+          <t>-31688.9912919164</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>5668.764</t>
+          <t>-28871.2803386592</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>5286.824</t>
+          <t>-21959.4349518166</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>5076.474</t>
+          <t>-18508.0317049809</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>5009.031</t>
+          <t>-18161.1274535988</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8318.716</t>
+          <t>-3803820133.80207</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>8152.208</t>
+          <t>-3730232542.64464</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>7925.622</t>
+          <t>-3835226612.80116</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>8148.436</t>
+          <t>-4623673752.5476</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>7899.596</t>
+          <t>-4492997253.1883</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>8574.16</t>
+          <t>-4573331872.31978</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8841.652</t>
+          <t>-5058455773.06314</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>9100.526</t>
+          <t>-5521576668.29016</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>8780.883</t>
+          <t>-5289174657.52305</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>8473.293</t>
+          <t>-4287207967.023</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>7691.174</t>
+          <t>-3571690424.52829</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>7468.977</t>
+          <t>-3504024068.62564</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>6654.112</t>
+          <t>-2719084968.95435</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>6825.378</t>
+          <t>-2836518905.22397</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>7174.205</t>
+          <t>-3101778125.56161</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.068</t>
+          <t>49138.6224887876</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>51251.8371137514</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>58609.3237655114</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>79422.5971296278</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>94869.4433031814</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>93943.5861021937</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.098</t>
+          <t>104989.483837322</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>117522.595477479</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>125135.669300996</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>112104.592855258</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.105</t>
+          <t>96153.0542095688</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>92631.5467073058</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>78664.6475174101</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>76998.5386028409</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>75153.5304209317</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>4333.492</t>
+          <t>0.0810468072412759</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>4262.373</t>
+          <t>0.0765052548720358</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>4227.828</t>
+          <t>0.0760709004903286</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>4231.829</t>
+          <t>0.10771248369124</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>4157.579</t>
+          <t>0.133086525853103</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>4511.771</t>
+          <t>0.113019474281926</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>4480.182</t>
+          <t>0.12536811668893</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>4540.935</t>
+          <t>0.136140000263265</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>4523.12</t>
+          <t>0.141884792808802</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>4501.571</t>
+          <t>0.124435480484063</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>4001.695</t>
+          <t>0.0900231702720148</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>3602.667</t>
+          <t>0.0903967953591256</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>3273.293</t>
+          <t>0.0801268887913688</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>3154.968</t>
+          <t>0.0865600124340603</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>3121.415</t>
+          <t>0.0853493685048142</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>40651.5387280451</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>42009.158390094</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>51107.8975575055</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>67263.2563442507</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>79781.2201755953</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>84935.0372807456</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>91741.8447831907</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>107502.82585072</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>121998.840506612</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>118382.472582558</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>0.055</t>
+          <t>108880.262444566</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>101977.329588734</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>84900.1206376122</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>78783.4538319716</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>77266.6846429039</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2345.829</t>
+          <t>56253.3941405882</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>2317.725</t>
+          <t>58357.7454758137</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2511.769</t>
+          <t>70766.9956743822</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2776.262</t>
+          <t>93810.7576750172</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>2895.056</t>
+          <t>110841.79911918</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>3071.444</t>
+          <t>122614.015466927</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>3237.878</t>
+          <t>129791.602927531</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>3316.263</t>
+          <t>150794.333058145</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>3330.185</t>
+          <t>168684.707020718</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>3259.905</t>
+          <t>160977.742863799</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>2815.827</t>
+          <t>147841.741793404</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>2629.693</t>
+          <t>139076.45011518</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>2151.981</t>
+          <t>115005.038162502</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>2026.404</t>
+          <t>106044.348720476</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>2063.932</t>
+          <t>103337.270128376</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>126.74</t>
+          <t>422177.192035329</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>134.24</t>
+          <t>451785.252831652</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>124.35</t>
+          <t>483856.45015616</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>107.39</t>
+          <t>516015.775403531</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>104.37</t>
+          <t>546921.425570403</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>98.92</t>
+          <t>560549.550997327</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>94.67</t>
+          <t>613615.906611696</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>95.41</t>
+          <t>650282.901088862</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>97.95</t>
+          <t>689927.048663309</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>99.12</t>
+          <t>698311.242184979</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>117.71</t>
+          <t>689525.663213687</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>115.57</t>
+          <t>667295.16834761</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>145.67</t>
+          <t>651113.190052215</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>150.52</t>
+          <t>647845.08654333</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>142.69</t>
+          <t>630182.428973513</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2.656</t>
+          <t>77998.0484887092</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>80585.1016106858</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2.419</t>
+          <t>88931.2452022611</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>1.864</t>
+          <t>95323.8177435567</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>1.582</t>
+          <t>99325.0856797766</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>1.632</t>
+          <t>106771.624364139</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>1.439</t>
+          <t>108323.425374842</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>1.278</t>
+          <t>110756.072124047</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>109835.766784289</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>106661.035695527</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>104374.730128624</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1.119</t>
+          <t>93837.5469144385</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>1.174</t>
+          <t>84732.9278439196</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>1.184</t>
+          <t>76827.8051207019</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>75335.3568540197</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>58041.7323200587</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>59715.4963829191</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>65728.2036048714</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>70303.6505527591</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>72807.0876694045</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>75080.9438388505</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>77416.5671222869</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>80425.0077014649</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>80233.046670096</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>78600.3705743841</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>76868.4304288061</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>68694.694681135</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>62296.173357718</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>57205.6957215441</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>56477.0145574304</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>61714.1815646216</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>62969.685322715</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>67098.56038985</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>87762.3660295679</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>106558.888679552</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>99856.9654623683</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>112598.947774323</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>130523.371579884</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>145798.780787111</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>135265.174584716</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>116825.106269167</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>114142.063060725</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>102100.043855909</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>106428.857446724</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>105006.742550827</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>5318839100</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>5428968500</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>5635052800</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>5757773200</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>5916714100</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>6109817400</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>6303115400</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>6480265600</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>6592100100</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>6491208300</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>6130235900</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>5668764100</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>5286824000</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>5076474500</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>5009031100</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>8733792982.43389</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>8744551595.55054</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>8938063789.37469</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>9052747770.11624</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>9228505989.84124</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>9814808490.6709</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>9900977076.97954</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>10052117686.2983</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>10122078805.7629</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>9982986459.87159</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>9297616177.50601</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>8652106004.09944</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>8042357542.78347</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>7729315520.0255</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>7625096110.78841</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>4333491918.53292</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>4262372547.55095</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4227828196.36898</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>4231829174.66202</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>4157579059.82458</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>4511770903.20096</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>4480181608.76682</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>4540934594.14305</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>4523120085.16713</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>4501570658.78583</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>4001695430.3924</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>3602666828.41571</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>3273293421.65186</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>3154968418.52305</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>3121414831.96669</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>4308120</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>4328410</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>4434300</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>4495720</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4604100</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>4648180</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>4731320</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>4795150</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>4856400</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>4829030</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>4705510</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>4381870</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>4105270</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>3957320</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>3962620</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2680940</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>2740560</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>2852710</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>2916130</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3013940</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>2952450</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>3069920</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>3151190</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>3214890</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3190810</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>3150020</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>2919820</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>2715750</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>2621850</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>2625170</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>8733792982.43389</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>8744551595.55054</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>8938063789.37469</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>9052747770.11624</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>9228505989.84124</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>9814808490.6709</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>9900977076.97954</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>10052117686.2983</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>10122078805.7629</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>9982986459.87159</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>9297616177.50601</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>8652106004.09944</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>8042357542.78347</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>7729315520.0255</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>7625096110.78841</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>5318839100</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>5428968500</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>5635052800</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>5757773200</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>5916714100</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>6109817400</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>6303115400</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>6480265600</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>6592100100</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>6491208300</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>6130235900</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>5668764100</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>5286824000</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>5076474500</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>5009031100</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>216384.626179433</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>222839.176974647</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>253427.303695132</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>324724.142117982</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>387847.130174357</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>399975.996473911</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>444439.543068724</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>517719.991568386</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>568356.966791784</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>524185.764184476</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>470137.276661896</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>449979.216539234</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>394295.267582509</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>383396.329357871</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>375244.052215509</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>117967.472659433</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>121327.484534647</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>137866.000495132</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>181572.818277982</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>217400.613164357</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>222470.794313911</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>242390.400028724</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>281317.923918386</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>314484.090831784</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>296242.805864476</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>264667.033661896</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>253218.067739234</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>217104.645182509</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>212473.312417871</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>208343.667265509</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>611602.77511175</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>656375.971185162</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>636557.74434621</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>545278.723603947</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>504051.071682229</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>496489.084088393</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>519681.949304858</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>484715.031124539</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>457919.04279428</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>473497.669151651</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>486800.208843456</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>446387.38751935</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>477781.982787537</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>482297.39846344</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>491691.200181293</t>
         </is>
       </c>
     </row>
@@ -2699,7 +4265,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2722,36 +4288,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -2763,331 +4344,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3124,6 +5069,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>WIOD16</t>
